--- a/Result.xlsx
+++ b/Result.xlsx
@@ -103,8 +103,10 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -154,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -177,6 +179,7 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" builtinId="0" name="Normal"/>
@@ -185,7 +188,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+      <x14ac:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -553,43 +556,43 @@
       <c r="B2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="8">
         <v>22.1126</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="8">
         <v>51.5666</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="8">
         <v>56.1836</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="8">
         <v>2.3293</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="8">
         <v>34.346</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="8">
         <v>53.3328</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="8">
         <v>12.8561</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="8">
         <v>12.35</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="8">
         <v>0.0009</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="8">
         <v>0.0035</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2" s="8">
         <v>2.2689</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2" s="8">
         <v>1.8285</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="8">
         <v>91.6225</v>
       </c>
     </row>
@@ -598,43 +601,43 @@
         <v>17</v>
       </c>
       <c r="B3" s="3"/>
-      <c r="C3" s="4">
+      <c r="C3" s="8">
         <v>2.9978</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="8">
         <v>1.8343</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="8">
         <v>9.4502</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="8">
         <v>2.3095</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="8">
         <v>2.736</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="8">
         <v>33.4588</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="8">
         <v>4.6309</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="8">
         <v>5.5694</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="8">
         <v>0.0005</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="8">
         <v>0.0017</v>
       </c>
-      <c r="M3" s="4">
+      <c r="M3" s="8">
         <v>2.2689</v>
       </c>
-      <c r="N3" s="4">
+      <c r="N3" s="8">
         <v>1.8285</v>
       </c>
-      <c r="O3" s="4">
+      <c r="O3" s="8">
         <v>10.6007</v>
       </c>
     </row>
@@ -645,43 +648,43 @@
       <c r="B4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="8">
         <v>0.9164</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="8">
         <v>1.6573</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="8">
         <v>8.5016</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="8">
         <v>0.0046</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="8">
         <v>1.096</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="8">
         <v>22.1887</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="8">
         <v>4.1608</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="8">
         <v>5.724</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="8">
         <v>0.0005</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="8">
         <v>0.0018</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="8">
         <v>0.0317</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4" s="8">
         <v>0.0144</v>
       </c>
-      <c r="O4" s="4">
+      <c r="O4" s="8">
         <v>6.7986</v>
       </c>
     </row>
@@ -690,43 +693,43 @@
         <v>20</v>
       </c>
       <c r="B5" s="3"/>
-      <c r="C5" s="4">
+      <c r="C5" s="8">
         <v>0.6295</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="8">
         <v>1.385</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="8">
         <v>7.9398</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="8">
         <v>0.0052</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="8">
         <v>2.893</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="8">
         <v>11.9854</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="8">
         <v>3.9165</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="8">
         <v>5.2095</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="8">
         <v>0.0005</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="8">
         <v>0.0018</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="8">
         <v>0.471</v>
       </c>
-      <c r="N5" s="4">
+      <c r="N5" s="8">
         <v>0.0074</v>
       </c>
-      <c r="O5" s="4">
+      <c r="O5" s="8">
         <v>6.9775</v>
       </c>
     </row>
@@ -735,43 +738,43 @@
         <v>21</v>
       </c>
       <c r="B6" s="3"/>
-      <c r="C6" s="4">
+      <c r="C6" s="8">
         <v>0.6034</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="8">
         <v>1.729</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="8">
         <v>7.7368</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="8">
         <v>0.0052</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="8">
         <v>2.9454</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="8">
         <v>11.3309</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="8">
         <v>3.9977</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="8">
         <v>5.1888</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="8">
         <v>0.0005</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="8">
         <v>0.0018</v>
       </c>
-      <c r="M6" s="4">
+      <c r="M6" s="8">
         <v>0.471</v>
       </c>
-      <c r="N6" s="4">
+      <c r="N6" s="8">
         <v>0.0074</v>
       </c>
-      <c r="O6" s="4">
+      <c r="O6" s="8">
         <v>7.2402</v>
       </c>
     </row>
@@ -780,43 +783,43 @@
         <v>22</v>
       </c>
       <c r="B7" s="3"/>
-      <c r="C7" s="4">
+      <c r="C7" s="8">
         <v>0.5772</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="8">
         <v>1.3861</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="8">
         <v>7.7871</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="8">
         <v>0.0052</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="8">
         <v>2.9176</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="8">
         <v>11.3901</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="8">
         <v>3.7208</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="8">
         <v>5.1629</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7" s="8">
         <v>0.0005</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7" s="8">
         <v>0.0018</v>
       </c>
-      <c r="M7" s="4">
+      <c r="M7" s="8">
         <v>0.471</v>
       </c>
-      <c r="N7" s="4">
+      <c r="N7" s="8">
         <v>0.0074</v>
       </c>
-      <c r="O7" s="4">
+      <c r="O7" s="8">
         <v>7.0143</v>
       </c>
     </row>
@@ -825,43 +828,43 @@
         <v>23</v>
       </c>
       <c r="B8" s="3"/>
-      <c r="C8" s="4">
+      <c r="C8" s="8">
         <v>0.5795</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="8">
         <v>1.4244</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="8">
         <v>7.7072</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="8">
         <v>0.0053</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="8">
         <v>2.9313</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="8">
         <v>11.2600</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="8">
         <v>3.7240</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="8">
         <v>5.1475</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8" s="8">
         <v>0.0005</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8" s="8">
         <v>0.0018</v>
       </c>
-      <c r="M8" s="4">
+      <c r="M8" s="8">
         <v>0.4710</v>
       </c>
-      <c r="N8" s="4">
+      <c r="N8" s="8">
         <v>0.0074</v>
       </c>
-      <c r="O8" s="4">
+      <c r="O8" s="8">
         <v>7.0763</v>
       </c>
     </row>
@@ -872,43 +875,43 @@
       <c r="B9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="8">
         <v>1.1740</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="8">
         <v>2.5918</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="8">
         <v>9.5546</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="8">
         <v>0.0083</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="8">
         <v>4.2078</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="8">
         <v>20.7708</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9" s="8">
         <v>4.6208</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="8">
         <v>6.0884</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9" s="8">
         <v>0.0005</v>
       </c>
-      <c r="L9" s="4">
+      <c r="L9" s="8">
         <v>0.0018</v>
       </c>
-      <c r="M9" s="4">
+      <c r="M9" s="8">
         <v>0.4665</v>
       </c>
-      <c r="N9" s="4">
+      <c r="N9" s="8">
         <v>0.0073</v>
       </c>
-      <c r="O9" s="4">
+      <c r="O9" s="8">
         <v>12.4936</v>
       </c>
     </row>
@@ -919,43 +922,43 @@
       <c r="B10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="8">
         <v>2.4933</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="8">
         <v>1.6456</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="8">
         <v>8.2393</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="8">
         <v>2.3315</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="8">
         <v>1.3939</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="8">
         <v>32.2659</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10" s="8">
         <v>4.4554</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="8">
         <v>5.5879</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K10" s="8">
         <v>0.0005</v>
       </c>
-      <c r="L10" s="4">
+      <c r="L10" s="8">
         <v>0.0017</v>
       </c>
-      <c r="M10" s="4">
+      <c r="M10" s="8">
         <v>1.8205</v>
       </c>
-      <c r="N10" s="4">
+      <c r="N10" s="8">
         <v>1.8285</v>
       </c>
-      <c r="O10" s="4">
+      <c r="O10" s="8">
         <v>8.8786</v>
       </c>
     </row>

--- a/Result.xlsx
+++ b/Result.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="45">
   <si>
     <t>方法</t>
   </si>
@@ -98,6 +98,57 @@
   </si>
   <si>
     <t>3位局部历史+10位PC</t>
+  </si>
+  <si>
+    <t>Perceptron</t>
+  </si>
+  <si>
+    <t>在线学习, HIST=20, TABLE=1024</t>
+  </si>
+  <si>
+    <t>Best方法</t>
+  </si>
+  <si>
+    <t>值(Row) = 所有方法最优</t>
+  </si>
+  <si>
+    <t>0.5772(R7)</t>
+  </si>
+  <si>
+    <t>1.3046(R11)</t>
+  </si>
+  <si>
+    <t>7.0186(R11)</t>
+  </si>
+  <si>
+    <t>0.0046(R4)</t>
+  </si>
+  <si>
+    <t>1.0960(R4)</t>
+  </si>
+  <si>
+    <t>11.2600(R8)</t>
+  </si>
+  <si>
+    <t>3.7208(R7)</t>
+  </si>
+  <si>
+    <t>5.0139(R11)</t>
+  </si>
+  <si>
+    <t>0.0005(R3)</t>
+  </si>
+  <si>
+    <t>0.0017(R3)</t>
+  </si>
+  <si>
+    <t>0.0317(R4)</t>
+  </si>
+  <si>
+    <t>0.0073(R9)</t>
+  </si>
+  <si>
+    <t>5.6642(R11)</t>
   </si>
 </sst>
 </file>
@@ -962,6 +1013,100 @@
         <v>8.8786</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11">
+        <v>0.6398</v>
+      </c>
+      <c r="D11">
+        <v>1.3046</v>
+      </c>
+      <c r="E11">
+        <v>7.0186</v>
+      </c>
+      <c r="F11">
+        <v>0.0046</v>
+      </c>
+      <c r="G11">
+        <v>3.0465</v>
+      </c>
+      <c r="H11">
+        <v>22.4782</v>
+      </c>
+      <c r="I11">
+        <v>3.8420</v>
+      </c>
+      <c r="J11">
+        <v>5.0139</v>
+      </c>
+      <c r="K11">
+        <v>0.0005</v>
+      </c>
+      <c r="L11">
+        <v>0.0018</v>
+      </c>
+      <c r="M11">
+        <v>0.5887</v>
+      </c>
+      <c r="N11">
+        <v>0.0094</v>
+      </c>
+      <c r="O11">
+        <v>5.6642</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" t="s">
+        <v>38</v>
+      </c>
+      <c r="J12" t="s">
+        <v>39</v>
+      </c>
+      <c r="K12" t="s">
+        <v>40</v>
+      </c>
+      <c r="L12" t="s">
+        <v>41</v>
+      </c>
+      <c r="M12" t="s">
+        <v>42</v>
+      </c>
+      <c r="N12" t="s">
+        <v>43</v>
+      </c>
+      <c r="O12" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Result.xlsx
+++ b/Result.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="60">
   <si>
     <t>方法</t>
   </si>
@@ -149,6 +149,51 @@
   </si>
   <si>
     <t>5.6642(R11)</t>
+  </si>
+  <si>
+    <t>TAGE</t>
+  </si>
+  <si>
+    <t>8表几何历史(4-168), BASE=8K, TBL=4K</t>
+  </si>
+  <si>
+    <t>0.2960(R13)</t>
+  </si>
+  <si>
+    <t>1.2342(R13)</t>
+  </si>
+  <si>
+    <t>7.0186(R11)</t>
+  </si>
+  <si>
+    <t>0.0046(R4)</t>
+  </si>
+  <si>
+    <t>1.0863(R13)</t>
+  </si>
+  <si>
+    <t>7.7478(R13)</t>
+  </si>
+  <si>
+    <t>3.5098(R13)</t>
+  </si>
+  <si>
+    <t>5.0139(R11)</t>
+  </si>
+  <si>
+    <t>0.0005(R3)</t>
+  </si>
+  <si>
+    <t>0.0017(R3)</t>
+  </si>
+  <si>
+    <t>0.0317(R4)</t>
+  </si>
+  <si>
+    <t>0.0073(R9)</t>
+  </si>
+  <si>
+    <t>2.5221(R13)</t>
   </si>
 </sst>
 </file>
@@ -1107,6 +1152,100 @@
         <v>44</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13">
+        <v>0.2960</v>
+      </c>
+      <c r="D13">
+        <v>1.2342</v>
+      </c>
+      <c r="E13">
+        <v>7.6211</v>
+      </c>
+      <c r="F13">
+        <v>0.0061</v>
+      </c>
+      <c r="G13">
+        <v>1.0863</v>
+      </c>
+      <c r="H13">
+        <v>7.7478</v>
+      </c>
+      <c r="I13">
+        <v>3.5098</v>
+      </c>
+      <c r="J13">
+        <v>5.1339</v>
+      </c>
+      <c r="K13">
+        <v>0.0005</v>
+      </c>
+      <c r="L13">
+        <v>0.0018</v>
+      </c>
+      <c r="M13">
+        <v>0.0860</v>
+      </c>
+      <c r="N13">
+        <v>0.0080</v>
+      </c>
+      <c r="O13">
+        <v>2.5221</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" t="s">
+        <v>51</v>
+      </c>
+      <c r="H14" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14" t="s">
+        <v>53</v>
+      </c>
+      <c r="J14" t="s">
+        <v>54</v>
+      </c>
+      <c r="K14" t="s">
+        <v>55</v>
+      </c>
+      <c r="L14" t="s">
+        <v>56</v>
+      </c>
+      <c r="M14" t="s">
+        <v>57</v>
+      </c>
+      <c r="N14" t="s">
+        <v>58</v>
+      </c>
+      <c r="O14" t="s">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Result.xlsx
+++ b/Result.xlsx
@@ -39,7 +39,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -56,6 +56,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00BDD7EE"/>
         <bgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -78,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -122,6 +128,17 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -487,7 +504,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.14785714285714" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
@@ -583,11 +600,16 @@
           <t>SHORT_MOBILE-30</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>备注(实验目标)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>static</t>
+          <t>static (always T)</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
@@ -634,245 +656,270 @@
       <c r="O2" s="4" t="n">
         <v>91.6225</v>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>基线对比</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>2bits  PC&gt;&gt; 2</t>
+          <t>1-bit</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>PHT 2^17×2bit = 32 KB</t>
+          <t>PHT 2^17×1bit = 16 KB</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2.9978</v>
+        <v>5.7367</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>1.8343</v>
+        <v>2.7511</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>9.450200000000001</v>
+        <v>12.1061</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>2.3095</v>
+        <v>4.6184</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>2.736</v>
+        <v>3.4558</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>33.4588</v>
+        <v>43.1709</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>4.6309</v>
+        <v>8.6464</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>5.5694</v>
-      </c>
-      <c r="K3" s="9" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="L3" s="9" t="n">
-        <v>0.0017</v>
+        <v>6.029</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>0.0035</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>2.2689</v>
+        <v>4.5242</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>1.8285</v>
+        <v>3.6568</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>10.6007</v>
+        <v>16.6573</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>目标1</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>local  PC&gt;&gt; 2</t>
+          <t>global (10位GHR)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>BHT 2^17×10bit + PHT 2^10×2bit = 160 KB</t>
+          <t>GHR 10bit + PHT 2^10×2bit ≈ 0.25 KB</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0.9164</v>
+        <v>1.174</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1.6573</v>
+        <v>2.5918</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>8.5016</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>0.0046</v>
-      </c>
-      <c r="G4" s="10" t="n">
-        <v>1.096</v>
+        <v>9.554600000000001</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>4.2078</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>22.1887</v>
+        <v>20.7708</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>4.1608</v>
+        <v>4.6208</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>5.724</v>
-      </c>
-      <c r="K4" s="10" t="n">
+        <v>6.0884</v>
+      </c>
+      <c r="K4" s="9" t="n">
         <v>0.0005</v>
       </c>
       <c r="L4" s="4" t="n">
         <v>0.0018</v>
       </c>
-      <c r="M4" s="9" t="n">
-        <v>0.0317</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>0.0144</v>
+      <c r="M4" s="4" t="n">
+        <v>0.4665</v>
+      </c>
+      <c r="N4" s="9" t="n">
+        <v>0.0073</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>6.7986</v>
+        <v>12.4936</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>目标2</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="19.5" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>gshare PC&gt;&gt;2</t>
+          <t>2bits PC&gt;&gt;2</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>GHR 17bit + PHT 2^17×2bit ≈ 32 KB</t>
+          <t>PHT 2^17×2bit = 32 KB</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.6294999999999999</v>
+        <v>2.9978</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1.385</v>
+        <v>1.8343</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>7.9398</v>
+        <v>9.450200000000001</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.0052</v>
+        <v>2.3095</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>2.893</v>
+        <v>2.736</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>11.9854</v>
+        <v>33.4588</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>3.9165</v>
+        <v>4.6309</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>5.2095</v>
-      </c>
-      <c r="K5" s="4" t="n">
+        <v>5.5694</v>
+      </c>
+      <c r="K5" s="15" t="n">
         <v>0.0005</v>
       </c>
-      <c r="L5" s="4" t="n">
-        <v>0.0018</v>
+      <c r="L5" s="9" t="n">
+        <v>0.0017</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.471</v>
-      </c>
-      <c r="N5" s="10" t="n">
-        <v>0.0074</v>
+        <v>2.2689</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>1.8285</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>6.9775</v>
+        <v>10.6007</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>目标3</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="19.5" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>gshare PC&gt;&gt;1</t>
+          <t>3-bit PC&gt;&gt;2</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>GHR 17bit + PHT 2^17×2bit ≈ 32 KB</t>
+          <t>PHT 2^17×3bit = 48 KB</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.6034</v>
+        <v>3.1499</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.729</v>
+        <v>1.7709</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7.7368</v>
+        <v>8.5304</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.0052</v>
+        <v>2.3095</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.9454</v>
+        <v>2.8277</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>11.3309</v>
+        <v>32.1861</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3.9977</v>
+        <v>4.511</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>5.1888</v>
+        <v>5.5021</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>0.0005</v>
       </c>
-      <c r="L6" s="4" t="n">
-        <v>0.0018</v>
+      <c r="L6" s="15" t="n">
+        <v>0.0017</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.471</v>
+        <v>2.2689</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.0074</v>
+        <v>1.8285</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>7.2402</v>
+        <v>10.987</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>目标4</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>gshare</t>
+          <t>local PC&gt;&gt;2</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>GHR 17bit + PHT 2^17×2bit ≈ 32 KB</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="n">
-        <v>0.5772</v>
+          <t>BHT 2^17×10bit + PHT 2^10×2bit = 160 KB</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>0.9164</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.3861</v>
+        <v>1.6573</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>7.7871</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>2.9176</v>
+        <v>8.5016</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>1.096</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>11.3901</v>
-      </c>
-      <c r="I7" s="10" t="n">
-        <v>3.7208</v>
+        <v>22.1887</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>4.1608</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.1629</v>
+        <v>5.724</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>0.0005</v>
@@ -880,101 +927,111 @@
       <c r="L7" s="4" t="n">
         <v>0.0018</v>
       </c>
-      <c r="M7" s="4" t="n">
-        <v>0.471</v>
+      <c r="M7" s="9" t="n">
+        <v>0.0317</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.0074</v>
+        <v>0.0144</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>7.0143</v>
+        <v>6.7986</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>目标5+7</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>gshare PC&lt;&lt;1</t>
+          <t>local (3位hist+10位PC)</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>GHR 17bit + PHT 2^17×2bit ≈ 32 KB</t>
+          <t>BHT 2^10×3bit + PHT 2^13×2bit ≈ 2.4 KB</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.5795</v>
+        <v>2.4933</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.4244</v>
+        <v>1.6456</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>7.7072</v>
+        <v>8.2393</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.0053</v>
+        <v>2.3315</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.9313</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>11.26</v>
+        <v>1.3939</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>32.2659</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3.724</v>
+        <v>4.4554</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.1475</v>
+        <v>5.5879</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>0.0005</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0018</v>
+        <v>0.0017</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.471</v>
+        <v>1.8205</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.0074</v>
+        <v>1.8285</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>7.0763</v>
+        <v>8.8786</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>目标5+7</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>gshare PC&gt;&gt;2</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>GHR 10bit + PHT 2^10×2bit ≈ 0.25 KB</t>
+          <t>GHR 17bit + PHT 2^17×2bit ≈ 32 KB</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.174</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2.5918</v>
+        <v>1.385</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>9.554600000000001</v>
+        <v>7.9398</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.0083</v>
+        <v>0.0052</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.2078</v>
+        <v>2.893</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>20.7708</v>
+        <v>11.9854</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.6208</v>
+        <v>3.9165</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>6.0884</v>
+        <v>5.2095</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0.0005</v>
@@ -983,100 +1040,110 @@
         <v>0.0018</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.4665</v>
-      </c>
-      <c r="N9" s="9" t="n">
-        <v>0.0073</v>
+        <v>0.471</v>
+      </c>
+      <c r="N9" s="15" t="n">
+        <v>0.0074</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>12.4936</v>
+        <v>6.9775</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>目标6</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>gshare PC&gt;&gt;1</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>BHT 2^10×3bit + PHT 2^13×2bit ≈ 2.4 KB</t>
+          <t>GHR 17bit + PHT 2^17×2bit ≈ 32 KB</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.4933</v>
+        <v>0.6034</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.6456</v>
+        <v>1.729</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>8.2393</v>
+        <v>7.7368</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.3315</v>
+        <v>0.0052</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.3939</v>
+        <v>2.9454</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>32.2659</v>
+        <v>11.3309</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.4554</v>
+        <v>3.9977</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>5.5879</v>
+        <v>5.1888</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>0.0005</v>
       </c>
-      <c r="L10" s="10" t="n">
-        <v>0.0017</v>
+      <c r="L10" s="4" t="n">
+        <v>0.0018</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.8205</v>
+        <v>0.471</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.8285</v>
+        <v>0.0074</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>8.8786</v>
+        <v>7.2402</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>目标6</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Perceptron</t>
+          <t>gshare (XOR)</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>weights 1024×21×8bit + GHR 20bit ≈ 21 KB</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>0.6398</v>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>1.3046</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>7.0186</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>0.0046</v>
+          <t>GHR 17bit + PHT 2^17×2bit ≈ 32 KB</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>0.5772</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1.3861</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>7.7871</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0.0052</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>3.0465</v>
+        <v>2.9176</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>22.4782</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>3.842</v>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>5.0139</v>
+        <v>11.3901</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>3.7208</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>5.1629</v>
       </c>
       <c r="K11" s="5" t="n">
         <v>0.0005</v>
@@ -1085,49 +1152,54 @@
         <v>0.0018</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>0.5887</v>
+        <v>0.471</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>0.0094</v>
-      </c>
-      <c r="O11" s="11" t="n">
-        <v>5.6642</v>
+        <v>0.0074</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>7.0143</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>目标6</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>TAGE</t>
+          <t>gshare PC&lt;&lt;1</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>BASE 8K×2bit + 8×TBL 4K×16bit + GHR 168bit ≈ 66 KB</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="n">
-        <v>0.296</v>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>1.2342</v>
-      </c>
-      <c r="E12" s="14" t="n">
-        <v>7.6211</v>
+          <t>GHR 17bit + PHT 2^17×2bit ≈ 32 KB</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>0.5795</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>1.4244</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>7.7072</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.0061</v>
-      </c>
-      <c r="G12" s="13" t="n">
-        <v>1.0863</v>
-      </c>
-      <c r="H12" s="13" t="n">
-        <v>7.7478</v>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>3.5098</v>
-      </c>
-      <c r="J12" s="14" t="n">
-        <v>5.1339</v>
+        <v>0.0053</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>2.9313</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>5.1475</v>
       </c>
       <c r="K12" s="8" t="n">
         <v>0.0005</v>
@@ -1135,93 +1207,190 @@
       <c r="L12" s="8" t="n">
         <v>0.0018</v>
       </c>
-      <c r="M12" s="14" t="n">
-        <v>0.08599999999999999</v>
+      <c r="M12" s="8" t="n">
+        <v>0.471</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="O12" s="13" t="n">
-        <v>2.5221</v>
+        <v>0.0074</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>7.0763</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>目标6</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="20.25" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
+          <t>Perceptron</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>weights 1024×21×8bit + GHR 20bit ≈ 21 KB</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.6398</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>1.3046</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>7.0186</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>3.0465</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>22.4782</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>3.842</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>5.0139</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>0.5887</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="O13" s="16" t="n">
+        <v>5.6642</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>目标6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TAGE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BASE 8K×2bit + 8×TBL 4K×16bit + GHR 168bit ≈ 66 KB</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>1.2342</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>7.6211</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>1.0863</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>7.7478</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>3.5098</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>5.1339</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="M14" s="19" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="O14" s="18" t="n">
+        <v>2.5221</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>目标6</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Best方法</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>值(Row) = 所有方法最优</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>0.2960(R13)</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>1.2342(R13)</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>7.0186(R11)</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>0.0046(R4)</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>1.0863(R13)</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>7.7478(R13)</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>3.5098(R13)</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>5.0139(R11)</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>0.0005(R3)</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>0.0017(R3)</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>0.0317(R4)</t>
-        </is>
-      </c>
-      <c r="N13" s="5" t="inlineStr">
-        <is>
-          <t>0.0073(R9)</t>
-        </is>
-      </c>
-      <c r="O13" s="5" t="inlineStr">
-        <is>
-          <t>2.5221(R13)</t>
-        </is>
-      </c>
-    </row>
+      <c r="C15" s="18" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>1.2342</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>7.0186</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>1.0863</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>7.7478</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>3.5098</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>5.0139</v>
+      </c>
+      <c r="K15" s="18" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="L15" s="18" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="M15" s="18" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="N15" s="18" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="O15" s="18" t="n">
+        <v>2.5221</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>汇总</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
